--- a/20240308_output_test/output/20240308_output_test_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_pairs.xlsx
@@ -7,10 +7,40 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ga1-Ga1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Co1B-Ga1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ga1-Ga1A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="La1-Ga1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ga1B-Ga2B" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CoA-Ga1B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CoA-Ga2B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CoA-CoA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ga1B-Ga1B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="La1-CoA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Co2A-Ga1B" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="La1-Ga1B" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Co2A-CoA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Rh1-Ge1" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ge1-Ge1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Ho1-Ge1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Co1B-Ga1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ga1-Ga1A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="La1-Ga1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Ga1-Ga1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Rh1-In2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Rh1-Rh1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="In2-In2" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="U-Rh1" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="U-In2" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Co1A-Ga2B" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Co1A-Co2A" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="La-Ga1B" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="La-Co1A" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Pt,Sn2-Pt,Sn2" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Pt,Sn1-Pt,Sn1" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Pt,Sn1-Pt,Sn2" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Sm1-Ge1" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Nd1-Ge1" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Ru1-Ge1" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Tb1-Ge1" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Pr1-Ge1" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Eu1-Ge1" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,6 +458,370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -455,6 +849,144 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,6 +1000,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1612190.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1612190.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1612190.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -497,15 +1167,475 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1612190.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1612190.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.141</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -543,15 +1673,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -589,15 +1964,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.291</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
